--- a/test_data/WTA/WTA Pillar2 Forms/WTA Pillar2 Forms_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Forms/WTA Pillar2 Forms_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -74,9 +69,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -620,17 +612,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>The forms table or its columns did not render as expected.</t>
+          <t>Selecting Australia rendered the forms table with the expected columns.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] Forms table with Title/Download/Project columns is visible</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[PASS] Forms table with Title/Download/Project columns is visible</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -678,17 +670,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>A form row was missing its download link or 'Add to Project' action.</t>
+          <t>Each form row exposed a download link and an 'Add to Project' action.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] A download link and an 'Add to Project' button are present</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>[PASS] A download link and an 'Add to Project' button are present</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -746,6 +738,66 @@
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>P2Forms_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 Forms</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>The 'English' download link triggers a real, non-empty file download</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the first 'English' download link must trigger a real download with no failure and a non-zero size - P2Forms_03 only proved the link is visible, not that it actually downloads anything.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Pillar 2 &gt; Forms.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Pillar 2 &gt; Forms
+2. Select Australia
+3. Click the first 'English' download link
+4. Verify a real, non-empty file download completed</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the first 'English' download link must trigger a real download with no failure and a non-zero size - P2Forms_03 only proved the link is visible, not that it actually downloads anything.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>The download link correctly downloaded 'AU_Form__NAT_0656_06_2025_English_pdf.pdf' (1056759 bytes).</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The 'English' download link produces a real, non-empty file with no failure</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 Forms/WTA Pillar2 Forms_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Forms/WTA Pillar2 Forms_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -60,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -69,6 +74,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -436,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2Forms_01</t>
+          <t>P2Forms_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,55 +530,55 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 &gt; Forms loads with the jurisdiction placeholder</t>
+          <t>Each form row has a Download link and an Add to Project button</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must load showing the left-panel instruction text.</t>
+          <t>For Australia, at least one row must show an 'English' download link and an 'Add to Project' button.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in, Australia selected on Pillar 2 &gt; Forms.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in and open Pillar 2 &gt; Forms
-2. Verify the placeholder text is visible</t>
+          <t>1. Log in, open Pillar 2 &gt; Forms, select Australia
+2. Verify an 'English' download link and an 'Add to Project' button are visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The page must load showing the left-panel instruction text.</t>
+          <t>For Australia, at least one row must show an 'English' download link and an 'Add to Project' button.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 &gt; Forms loaded with the placeholder visible.</t>
+          <t>A form row was missing its download link or 'Add to Project' action.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Placeholder instruction text is visible</t>
+          <t>[FAIL] A download link and an 'Add to Project' button are present</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2Forms_02</t>
+          <t>P2Forms_04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,12 +588,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction renders the forms table</t>
+          <t>Switching region tabs hides out-of-region countries</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Checking 'Australia' must render a 'Showing forms of Australia' table with the expected columns.</t>
+          <t>Clicking 'Americas' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -595,209 +603,32 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Pillar 2 &gt; Forms
-2. Check 'Australia'
-3. Verify the forms table and its column headers are visible</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' must render a 'Showing forms of Australia' table with the expected columns.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia rendered the forms table with the expected columns.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Forms table with Title/Download/Project columns is visible</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P2Forms_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Forms</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Each form row has a Download link and an Add to Project button</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>For Australia, at least one row must show an 'English' download link and an 'Add to Project' button.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; Forms.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Pillar 2 &gt; Forms, select Australia
-2. Verify an 'English' download link and an 'Add to Project' button are visible</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>For Australia, at least one row must show an 'English' download link and an 'Add to Project' button.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Each form row exposed a download link and an 'Add to Project' action.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] A download link and an 'Add to Project' button are present</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P2Forms_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Forms</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Switching region tabs hides out-of-region countries</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Americas' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Pillar 2 &gt; Forms.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Pillar 2 &gt; Forms
 2. Click the 'Americas' region tab
 3. Verify 'Australia' is no longer listed</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Americas' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Switching to 'Americas' hid 'Australia' from the jurisdiction list.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Australia' is not listed under 'Americas'</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P2Forms_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Forms</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>The 'English' download link triggers a real, non-empty file download</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the first 'English' download link must trigger a real download with no failure and a non-zero size - P2Forms_03 only proved the link is visible, not that it actually downloads anything.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; Forms.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Pillar 2 &gt; Forms
-2. Select Australia
-3. Click the first 'English' download link
-4. Verify a real, non-empty file download completed</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the first 'English' download link must trigger a real download with no failure and a non-zero size - P2Forms_03 only proved the link is visible, not that it actually downloads anything.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>The download link correctly downloaded 'AU_Form__NAT_0656_06_2025_English_pdf.pdf' (1056759 bytes).</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The 'English' download link produces a real, non-empty file with no failure</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 Forms/WTA Pillar2 Forms_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Forms/WTA Pillar2 Forms_Test_Cases.xlsx
@@ -44,12 +44,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2Forms_03</t>
+          <t>P2Forms_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -530,55 +530,55 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Each form row has a Download link and an Add to Project button</t>
+          <t>Pillar 2 &gt; Forms loads with the jurisdiction placeholder</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>For Australia, at least one row must show an 'English' download link and an 'Add to Project' button.</t>
+          <t>The page must load showing the left-panel instruction text.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; Forms.</t>
+          <t>User is logged in.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open Pillar 2 &gt; Forms, select Australia
-2. Verify an 'English' download link and an 'Add to Project' button are visible</t>
+          <t>1. Log in and open Pillar 2 &gt; Forms
+2. Verify the placeholder text is visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>For Australia, at least one row must show an 'English' download link and an 'Add to Project' button.</t>
+          <t>The page must load showing the left-panel instruction text.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>A form row was missing its download link or 'Add to Project' action.</t>
+          <t>Pillar 2 &gt; Forms loaded with the placeholder visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] A download link and an 'Add to Project' button are present</t>
+          <t>[PASS] Placeholder instruction text is visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2Forms_04</t>
+          <t>P2Forms_02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Switching region tabs hides out-of-region countries</t>
+          <t>Selecting a jurisdiction renders the forms table</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Americas' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
+          <t>Checking 'Australia' must render a 'Showing forms of Australia' table with the expected columns.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -603,34 +603,34 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Pillar 2 &gt; Forms
-2. Click the 'Americas' region tab
-3. Verify 'Australia' is no longer listed</t>
+2. Check 'Australia'
+3. Verify the forms table and its column headers are visible</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Americas' must hide 'Australia' (Asia Pacific) from the jurisdiction list.</t>
+          <t>Checking 'Australia' must render a 'Showing forms of Australia' table with the expected columns.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Switching to 'Americas' hid 'Australia' from the jurisdiction list.</t>
+          <t>The forms table or its columns did not render as expected.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Australia' is not listed under 'Americas'</t>
+          <t>[FAIL] Forms table with Title/Download/Project columns is visible</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
